--- a/ig/DM-JANVIER-2026/ValueSet-jdv-j387-role-participant-ms.xlsx
+++ b/ig/DM-JANVIER-2026/ValueSet-jdv-j387-role-participant-ms.xlsx
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Niveau ou situation scolaire de l'usager.</t>
+    <t>Rôle du participant vis à vis de l'événement (mandataire judiciaire, structure en charge de l'événement).</t>
   </si>
   <si>
     <t>Purpose</t>
